--- a/config/Coding/VF5NP_MHU_F115_v1.xlsx
+++ b/config/Coding/VF5NP_MHU_F115_v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\REDO\CODINGTOOL\config\Coding\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD11418E-9649-4020-88AD-DAD95B6FC177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C96A6C4-82B6-4EBD-8E80-FD16473A3D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90AE59FF-2EC9-4D60-A579-D965726AE335}"/>
   </bookViews>
